--- a/Excel/ExclusiveMaterialConfig.xlsx
+++ b/Excel/ExclusiveMaterialConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -82,19 +82,37 @@
     <t>string</t>
   </si>
   <si>
-    <t>鸡毛</t>
-  </si>
-  <si>
-    <t>鸡蛋</t>
-  </si>
-  <si>
-    <t>鸡冠</t>
-  </si>
-  <si>
-    <t>鹿角</t>
-  </si>
-  <si>
-    <t>鹿茸</t>
+    <t>狼毛</t>
+  </si>
+  <si>
+    <t>蛛丝</t>
+  </si>
+  <si>
+    <t>雄狮利爪</t>
+  </si>
+  <si>
+    <t>虫卵</t>
+  </si>
+  <si>
+    <t>蛇皮</t>
+  </si>
+  <si>
+    <t>巨鳄之泪</t>
+  </si>
+  <si>
+    <t>乌鸦羽</t>
+  </si>
+  <si>
+    <t>蝙蝠牙</t>
+  </si>
+  <si>
+    <t>尸王之心</t>
+  </si>
+  <si>
+    <t>树叶</t>
+  </si>
+  <si>
+    <t>鱼鳞</t>
   </si>
   <si>
     <t>鹿血</t>
@@ -110,7 +128,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,6 +150,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -276,12 +301,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -611,143 +636,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1242,12 +1268,90 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1"/>
-    <row r="13" s="1" customFormat="1" customHeight="1"/>
-    <row r="14" s="1" customFormat="1" customHeight="1"/>
-    <row r="15" s="1" customFormat="1" customHeight="1"/>
-    <row r="16" s="1" customFormat="1" customHeight="1"/>
-    <row r="17" s="1" customFormat="1" customHeight="1"/>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1">
+        <v>40000007</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1">
+        <v>40000008</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1">
+        <v>40000009</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1">
+        <v>40000010</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
+        <v>40000011</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1">
+        <v>40000012</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="1">
+        <v>6</v>
+      </c>
+    </row>
     <row r="18" s="1" customFormat="1" customHeight="1"/>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
     <row r="20" s="1" customFormat="1" customHeight="1"/>

--- a/Excel/ExclusiveMaterialConfig.xlsx
+++ b/Excel/ExclusiveMaterialConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -59,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>ID</t>
   </si>
@@ -116,6 +121,24 @@
   </si>
   <si>
     <t>鹿血</t>
+  </si>
+  <si>
+    <t>骨弓</t>
+  </si>
+  <si>
+    <t>骨杖</t>
+  </si>
+  <si>
+    <t>骨龙核心</t>
+  </si>
+  <si>
+    <t>獠牙</t>
+  </si>
+  <si>
+    <t>图腾</t>
+  </si>
+  <si>
+    <t>酋长重锤</t>
   </si>
 </sst>
 </file>
@@ -301,12 +324,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1352,12 +1375,90 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1"/>
-    <row r="19" s="1" customFormat="1" customHeight="1"/>
-    <row r="20" s="1" customFormat="1" customHeight="1"/>
-    <row r="21" s="1" customFormat="1" customHeight="1"/>
-    <row r="22" s="1" customFormat="1" customHeight="1"/>
-    <row r="23" s="1" customFormat="1" customHeight="1"/>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1">
+        <v>40000013</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1">
+        <v>40000014</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1">
+        <v>40000015</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1">
+        <v>40000016</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1">
+        <v>40000017</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1">
+        <v>40000018</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" s="1">
+        <v>6</v>
+      </c>
+    </row>
     <row r="24" s="1" customFormat="1" customHeight="1"/>
     <row r="25" s="1" customFormat="1" customHeight="1"/>
     <row r="26" s="1" customFormat="1" customHeight="1"/>

--- a/Excel/ExclusiveMaterialConfig.xlsx
+++ b/Excel/ExclusiveMaterialConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -139,6 +139,15 @@
   </si>
   <si>
     <t>酋长重锤</t>
+  </si>
+  <si>
+    <t>血花露</t>
+  </si>
+  <si>
+    <t>火甲虫</t>
+  </si>
+  <si>
+    <t>炎魔火髓</t>
   </si>
 </sst>
 </file>
@@ -1459,9 +1468,48 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1"/>
-    <row r="25" s="1" customFormat="1" customHeight="1"/>
-    <row r="26" s="1" customFormat="1" customHeight="1"/>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1">
+        <v>40000019</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1">
+        <v>40000020</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C26" s="1">
+        <v>21</v>
+      </c>
+      <c r="D26" s="1">
+        <v>40000021</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="1">
+        <v>6</v>
+      </c>
+    </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
     <row r="28" s="1" customFormat="1" customHeight="1"/>
     <row r="29" s="1" customFormat="1" customHeight="1"/>

--- a/Excel/ExclusiveMaterialConfig.xlsx
+++ b/Excel/ExclusiveMaterialConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -148,6 +148,44 @@
   </si>
   <si>
     <t>炎魔火髓</t>
+  </si>
+  <si>
+    <t>‌冰蝎爪</t>
+  </si>
+  <si>
+    <t>龙龟蛋</t>
+  </si>
+  <si>
+    <t>冰兽魔核</t>
+  </si>
+  <si>
+    <t>鬼面毒囊</t>
+  </si>
+  <si>
+    <t>巨蜥毒牙</t>
+  </si>
+  <si>
+    <t>暗影徽记</t>
+  </si>
+  <si>
+    <t>巨熊掌</t>
+  </si>
+  <si>
+    <r>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>狂暴牛角</t>
+    </r>
+  </si>
+  <si>
+    <t>亲卫令牌</t>
   </si>
 </sst>
 </file>
@@ -160,7 +198,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +225,18 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -668,137 +718,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -806,6 +856,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1125,7 +1177,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1510,12 +1562,132 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1"/>
-    <row r="28" s="1" customFormat="1" customHeight="1"/>
-    <row r="29" s="1" customFormat="1" customHeight="1"/>
-    <row r="30" s="1" customFormat="1" customHeight="1"/>
-    <row r="31" s="1" customFormat="1" customHeight="1"/>
-    <row r="32" s="1" customFormat="1" customHeight="1"/>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1">
+        <v>40000022</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1">
+        <v>40000023</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <v>40000024</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1">
+        <v>40000025</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <v>40000026</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1">
+        <v>40000027</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:6">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1">
+        <v>40000028</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:6">
+      <c r="C34" s="1">
+        <v>29</v>
+      </c>
+      <c r="D34" s="1">
+        <v>40000029</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F34" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:6">
+      <c r="C35" s="1">
+        <v>30</v>
+      </c>
+      <c r="D35" s="1">
+        <v>40000030</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" s="1">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">

--- a/Excel/ExclusiveMaterialConfig.xlsx
+++ b/Excel/ExclusiveMaterialConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
@@ -172,6 +172,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>‌</t>
     </r>
     <r>
@@ -186,6 +192,24 @@
   </si>
   <si>
     <t>亲卫令牌</t>
+  </si>
+  <si>
+    <t>魔瞳</t>
+  </si>
+  <si>
+    <t>血镰刀</t>
+  </si>
+  <si>
+    <t>神秘法杖</t>
+  </si>
+  <si>
+    <t>犬牙</t>
+  </si>
+  <si>
+    <t>恶魔利爪</t>
+  </si>
+  <si>
+    <t>深渊巨刃</t>
   </si>
 </sst>
 </file>
@@ -1177,7 +1201,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1688,6 +1712,90 @@
         <v>6</v>
       </c>
     </row>
+    <row r="36" customHeight="1" spans="3:6">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1">
+        <v>40000031</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:6">
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1">
+        <v>40000032</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:6">
+      <c r="C38" s="1">
+        <v>33</v>
+      </c>
+      <c r="D38" s="1">
+        <v>40000033</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:6">
+      <c r="C39" s="1">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1">
+        <v>40000034</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:6">
+      <c r="C40" s="1">
+        <v>35</v>
+      </c>
+      <c r="D40" s="1">
+        <v>40000035</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F40" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:6">
+      <c r="C41" s="1">
+        <v>36</v>
+      </c>
+      <c r="D41" s="1">
+        <v>40000036</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" s="1">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">
